--- a/data/horarios-141-2026-01-10.xlsx
+++ b/data/horarios-141-2026-01-10.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LP1912" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LP1912-215" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6203-6173" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="LP1912" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="LP1912-215" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="6203-6173" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 13:52:16</t>
+          <t>Actualizado: 14:10:16</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 13</t>
+          <t>16 únicos (por Identificador)</t>
         </is>
       </c>
     </row>
@@ -483,6 +483,11 @@
           <t>CodigoColectivo</t>
         </is>
       </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Identificador</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -509,6 +514,7 @@
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -535,6 +541,7 @@
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -561,6 +568,7 @@
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -587,6 +595,7 @@
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -613,6 +622,7 @@
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -639,6 +649,7 @@
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -665,6 +676,7 @@
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -691,6 +703,7 @@
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -717,6 +730,7 @@
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -743,6 +757,7 @@
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -769,6 +784,7 @@
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -795,6 +811,7 @@
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -821,6 +838,88 @@
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>14:10:09</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>11_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>15</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>14:10:09</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>24</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>14:10:09</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>39</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -833,7 +932,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -846,14 +945,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 13:52:16</t>
+          <t>Actualizado: 14:10:16</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 1</t>
+          <t>1 únicos (por Identificador)</t>
         </is>
       </c>
     </row>
@@ -888,6 +987,11 @@
           <t>CodigoColectivo</t>
         </is>
       </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Identificador</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -914,6 +1018,7 @@
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -926,7 +1031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -939,14 +1044,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 13:52:16</t>
+          <t>Actualizado: 14:10:16</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 3</t>
+          <t>4 únicos (por Identificador)</t>
         </is>
       </c>
     </row>
@@ -981,6 +1086,11 @@
           <t>CodigoColectivo</t>
         </is>
       </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Identificador</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1007,6 +1117,7 @@
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1033,6 +1144,7 @@
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1059,6 +1171,34 @@
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>14:10:16</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>215A_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>50</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>L6173</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/horarios-141-2026-01-10.xlsx
+++ b/data/horarios-141-2026-01-10.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Actualizado: 14:10:16</t>
+          <t>Última actualización: 15:05:43</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>16 únicos (por Identificador)</t>
+          <t>Total filas: 27</t>
         </is>
       </c>
     </row>
@@ -920,6 +920,303 @@
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>15:05:02</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>29</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>15:05:02</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>27_EL RETIRO</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>52</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>15:05:02</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>53</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>15:05:02</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>15_ABASTO</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>57</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>15:05:02</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>72</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>15:05:02</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>11_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>80</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>15:05:02</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>16:29</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>15_ABASTO</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>84</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>15:05:02</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>16_P MOR-SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>87</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>15:05:02</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>16:34</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>89</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>15:05:02</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>16:35</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>225_GOMEZ</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>90</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>15:05:02</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>16:41</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>17X38_ROMERO</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>96</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -945,14 +1242,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Actualizado: 14:10:16</t>
+          <t>Última actualización: 15:05:43</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>1 únicos (por Identificador)</t>
+          <t>Total filas: 1</t>
         </is>
       </c>
     </row>
@@ -1031,7 +1328,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1044,14 +1341,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Actualizado: 14:10:16</t>
+          <t>Última actualización: 15:05:43</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>4 únicos (por Identificador)</t>
+          <t>Total filas: 7</t>
         </is>
       </c>
     </row>
@@ -1199,6 +1496,87 @@
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>15:05:22</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>215C_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>48</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>L6203</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>15:05:43</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>215A_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>3</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>L6173</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>15:05:43</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>215B_LP-P MOR-1 Y 57</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>81</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>L6173</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/horarios-141-2026-01-10.xlsx
+++ b/data/horarios-141-2026-01-10.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 15:05:43</t>
+          <t>Última actualización: 15:13:09</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 27</t>
+          <t>Total filas: 35</t>
         </is>
       </c>
     </row>
@@ -1217,6 +1217,222 @@
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>15:12:29</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>21</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>15:12:29</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>45</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>15:12:29</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>15_ABASTO</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>49</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>15:12:29</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>64</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>15:12:29</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>16_P MOR-SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>79</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>15:12:29</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>81</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>15:12:29</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>16:34</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>225_GOMEZ</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>82</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>15:12:29</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>16:39</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>17X38_ROMERO</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>87</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1242,7 +1458,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 15:05:43</t>
+          <t>Última actualización: 15:13:09</t>
         </is>
       </c>
     </row>
@@ -1328,7 +1544,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1341,14 +1557,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 15:05:43</t>
+          <t>Última actualización: 15:13:09</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 7</t>
+          <t>Total filas: 8</t>
         </is>
       </c>
     </row>
@@ -1577,6 +1793,33 @@
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>15:12:49</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>215C_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>40</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>L6203</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/horarios-141-2026-01-10.xlsx
+++ b/data/horarios-141-2026-01-10.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 15:13:09</t>
+          <t>Última actualización: 15:16:35</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 35</t>
+          <t>Total filas: 39</t>
         </is>
       </c>
     </row>
@@ -1433,6 +1433,114 @@
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>15:15:54</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>11_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>9</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>15:15:54</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>59</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>15:15:54</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>16:37</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>15_ABASTO</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>82</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>15:15:54</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>16:53</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>98</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1458,7 +1566,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 15:13:09</t>
+          <t>Última actualización: 15:16:35</t>
         </is>
       </c>
     </row>
@@ -1544,7 +1652,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1557,14 +1665,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 15:13:09</t>
+          <t>Última actualización: 15:16:35</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 8</t>
+          <t>Total filas: 9</t>
         </is>
       </c>
     </row>
@@ -1820,6 +1928,33 @@
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>15:16:14</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>215C_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>35</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>L6203</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/horarios-141-2026-01-10.xlsx
+++ b/data/horarios-141-2026-01-10.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:G47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 15:16:35</t>
+          <t>Última actualización: 15:21:58</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 39</t>
+          <t>Total filas: 42</t>
         </is>
       </c>
     </row>
@@ -1541,6 +1541,87 @@
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>15:21:17</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>17X38_ROMERO</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>79</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>15:21:17</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>16:41</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>15_ABASTO</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>80</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>15:21:17</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>16:54</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>93</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1566,7 +1647,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 15:16:35</t>
+          <t>Última actualización: 15:21:58</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1733,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1665,14 +1746,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 15:16:35</t>
+          <t>Última actualización: 15:21:58</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 9</t>
+          <t>Total filas: 11</t>
         </is>
       </c>
     </row>
@@ -1955,6 +2036,60 @@
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>15:21:37</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>215C_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>28</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>L6203</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>15:21:58</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>215B_LP-P MOR-1 Y 57</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>64</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>L6173</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/horarios-141-2026-01-10.xlsx
+++ b/data/horarios-141-2026-01-10.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G47"/>
+  <dimension ref="A1:G50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 15:21:58</t>
+          <t>Última actualización: 15:29:13</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 42</t>
+          <t>Total filas: 45</t>
         </is>
       </c>
     </row>
@@ -1622,6 +1622,87 @@
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>15:28:32</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>11_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>2</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>15:28:32</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>17X38_ROMERO</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>70</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>15:28:32</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>17:03</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>14_ABASTO</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>95</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1647,7 +1728,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 15:21:58</t>
+          <t>Última actualización: 15:29:13</t>
         </is>
       </c>
     </row>
@@ -1746,7 +1827,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 15:21:58</t>
+          <t>Última actualización: 15:29:13</t>
         </is>
       </c>
     </row>

--- a/data/horarios-141-2026-01-10.xlsx
+++ b/data/horarios-141-2026-01-10.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:G60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 15:29:13</t>
+          <t>Última actualización: 15:53:49</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 45</t>
+          <t>Total filas: 55</t>
         </is>
       </c>
     </row>
@@ -1703,6 +1703,276 @@
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>15:53:08</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>2</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>15:53:08</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>16:04</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>11</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>15:53:08</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>22</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>15:53:08</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>29</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>15:53:08</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>16:37</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>17X38_ROMERO</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>44</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>15:53:08</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>16:52</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>59</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>15:53:08</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>14_ABASTO</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>72</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>15:53:08</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>15_ABASTO</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>75</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>15:53:08</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>11_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>92</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>15:53:08</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>17:28</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>15_ABASTO</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>95</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1728,7 +1998,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 15:29:13</t>
+          <t>Última actualización: 15:53:49</t>
         </is>
       </c>
     </row>
@@ -1814,7 +2084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1827,14 +2097,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 15:29:13</t>
+          <t>Última actualización: 15:53:49</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 11</t>
+          <t>Total filas: 12</t>
         </is>
       </c>
     </row>
@@ -2171,6 +2441,33 @@
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>15:53:29</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>215C_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>72</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>L6203</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/horarios-141-2026-01-10.xlsx
+++ b/data/horarios-141-2026-01-10.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G60"/>
+  <dimension ref="A1:G69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 15:53:49</t>
+          <t>Última actualización: 16:16:09</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 55</t>
+          <t>Total filas: 64</t>
         </is>
       </c>
     </row>
@@ -1973,6 +1973,249 @@
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>16:15:28</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>16:42</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>27</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>16:15:28</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>17:02</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>47</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>16:15:28</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>60</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>16:15:28</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>17:32</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>77</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>16:15:28</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>17:36</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>16_P MOR-SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>81</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>16:15:28</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>215B_EL PATO</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>90</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>16:15:28</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>17X38_ROMERO</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>91</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>16:15:28</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>17:47</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>27_EL RETIRO</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>92</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>16:15:28</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>17:51</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>215_EL PELIGRO</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>96</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1985,7 +2228,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1998,14 +2241,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 15:53:49</t>
+          <t>Última actualización: 16:16:09</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 1</t>
+          <t>Total filas: 3</t>
         </is>
       </c>
     </row>
@@ -2072,6 +2315,60 @@
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>16:15:28</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>215B_EL PATO</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>90</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>16:15:28</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>17:51</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>215_EL PELIGRO</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>96</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2084,7 +2381,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2097,14 +2394,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 15:53:49</t>
+          <t>Última actualización: 16:16:09</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 12</t>
+          <t>Total filas: 13</t>
         </is>
       </c>
     </row>
@@ -2468,6 +2765,33 @@
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>16:15:49</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>17:04</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>215C_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>49</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>L6203</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/horarios-141-2026-01-10.xlsx
+++ b/data/horarios-141-2026-01-10.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G69"/>
+  <dimension ref="A1:G82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 16:16:09</t>
+          <t>Última actualización: 16:30:39</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 64</t>
+          <t>Total filas: 77</t>
         </is>
       </c>
     </row>
@@ -2216,6 +2216,357 @@
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>16:29:52</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>17X38_ROMERO</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>7</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>16:29:52</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>22</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>16:29:52</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>16:57</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>28</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>16:29:52</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>17:01</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>32</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>16:29:52</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>17:07</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>15_ABASTO</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>38</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>16:29:52</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>17:14</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>45</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>16:29:52</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>54</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>16:29:52</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>17:27</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>15_ABASTO</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>58</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>16:29:52</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>17:34</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>65</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>16:29:52</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>17:34</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>65</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>16:29:52</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>16_P MOR-SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>66</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>16:29:52</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>17:49</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>27_EL RETIRO</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>80</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>16:29:52</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>18:05</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>14_ABASTO</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>96</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2241,7 +2592,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 16:16:09</t>
+          <t>Última actualización: 16:30:39</t>
         </is>
       </c>
     </row>
@@ -2394,7 +2745,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 16:16:09</t>
+          <t>Última actualización: 16:30:39</t>
         </is>
       </c>
     </row>

--- a/data/horarios-141-2026-01-10.xlsx
+++ b/data/horarios-141-2026-01-10.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G82"/>
+  <dimension ref="A1:G86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 16:30:39</t>
+          <t>Última actualización: 16:43:09</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 77</t>
+          <t>Total filas: 81</t>
         </is>
       </c>
     </row>
@@ -2567,6 +2567,114 @@
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>16:42:23</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>28</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>16:42:23</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>17:24</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>42</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>16:42:23</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>17:33</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>51</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>16:42:23</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>17:39</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>17X38_ROMERO</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>57</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2592,7 +2700,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 16:30:39</t>
+          <t>Última actualización: 16:43:09</t>
         </is>
       </c>
     </row>
@@ -2732,7 +2840,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2745,14 +2853,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 16:30:39</t>
+          <t>Última actualización: 16:43:09</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 13</t>
+          <t>Total filas: 14</t>
         </is>
       </c>
     </row>
@@ -3143,6 +3251,33 @@
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>16:42:44</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>16:59</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>215C_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>17</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>L6203</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/horarios-141-2026-01-10.xlsx
+++ b/data/horarios-141-2026-01-10.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G86"/>
+  <dimension ref="A1:G94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 16:43:09</t>
+          <t>Última actualización: 16:53:21</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 81</t>
+          <t>Total filas: 89</t>
         </is>
       </c>
     </row>
@@ -2675,6 +2675,222 @@
       </c>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>16:52:35</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>16:54</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>15_ABASTO</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>2</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>16:52:35</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>17:04</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>12</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>16:52:35</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>28</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>16:52:35</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>17:37</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>27_EL RETIRO</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>45</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>16:52:35</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>17:38</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>17X38_ROMERO</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>46</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>16:52:35</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>56</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>16:52:35</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>18:08</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>76</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>16:52:35</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>18:14</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>82</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2700,7 +2916,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 16:43:09</t>
+          <t>Última actualización: 16:53:21</t>
         </is>
       </c>
     </row>
@@ -2840,7 +3056,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2853,14 +3069,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 16:43:09</t>
+          <t>Última actualización: 16:53:21</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 14</t>
+          <t>Total filas: 15</t>
         </is>
       </c>
     </row>
@@ -3278,6 +3494,33 @@
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>16:52:56</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>16:57</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>215C_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>5</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>L6203</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/horarios-141-2026-01-10.xlsx
+++ b/data/horarios-141-2026-01-10.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G94"/>
+  <dimension ref="A1:G110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 16:53:21</t>
+          <t>Última actualización: 17:22:42</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 89</t>
+          <t>Total filas: 105</t>
         </is>
       </c>
     </row>
@@ -2891,6 +2891,438 @@
       </c>
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>17:21:56</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>17:24</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>11_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>3</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>17:21:56</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>17:36</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>27_EL RETIRO</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>15</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>17:21:56</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>17:47</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>26</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>17:21:56</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>27</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>17:21:56</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>18:03</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>42</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>17:21:56</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>18:04</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>14_ABASTO</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>43</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>17:21:56</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>61</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>17:21:56</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>18:24</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>11_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>63</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>17:21:56</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>18:27</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>15_ABASTO</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>66</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>17:21:56</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>18:33</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>72</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>17:21:56</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>18:34</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>14X44_ABASTO</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>73</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>17:21:56</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>18:38</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>17X38_ROMERO</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>77</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>17:21:56</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>18:41</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>16_P MOR-SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>80</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>17:21:56</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>18:41</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>14_ABASTO</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>80</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr"/>
+      <c r="G108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>17:21:56</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>18:51</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>15_ABASTO</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>90</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr"/>
+      <c r="G109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>17:21:56</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>18:59</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>98</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2916,7 +3348,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 16:53:21</t>
+          <t>Última actualización: 17:22:42</t>
         </is>
       </c>
     </row>
@@ -3056,7 +3488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3069,14 +3501,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 16:53:21</t>
+          <t>Última actualización: 17:22:42</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 15</t>
+          <t>Total filas: 16</t>
         </is>
       </c>
     </row>
@@ -3521,6 +3953,33 @@
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>17:22:17</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>215C_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>60</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>L6203</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/horarios-141-2026-01-10.xlsx
+++ b/data/horarios-141-2026-01-10.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G110"/>
+  <dimension ref="A1:G122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 17:22:42</t>
+          <t>Última actualización: 17:43:48</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 105</t>
+          <t>Total filas: 117</t>
         </is>
       </c>
     </row>
@@ -3323,6 +3323,330 @@
       </c>
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>17:43:07</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>18:01</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>18</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr"/>
+      <c r="G111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>17:43:07</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>18:04</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>21</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr"/>
+      <c r="G112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>17:43:07</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>18:28</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>15_ABASTO</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>45</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr"/>
+      <c r="G113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>17:43:07</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>18:39</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>17X38_ROMERO</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>56</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>17:43:07</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>18:42</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>16_P MOR-SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>59</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>17:43:07</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>14_ABASTO</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>62</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr"/>
+      <c r="G116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>17:43:07</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>18:52</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>15_ABASTO</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>69</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr"/>
+      <c r="G117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>17:43:07</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>77</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr"/>
+      <c r="G118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>17:43:07</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>19:02</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>17_ROMERO</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>79</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>17:43:07</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>19:04</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>81</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>17:43:07</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>19:12</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>81_EL PELIGRO</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>89</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr"/>
+      <c r="G121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>17:43:07</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>215C_EL PATO</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>98</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3335,7 +3659,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3348,14 +3672,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 17:22:42</t>
+          <t>Última actualización: 17:43:48</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 3</t>
+          <t>Total filas: 4</t>
         </is>
       </c>
     </row>
@@ -3476,6 +3800,33 @@
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>17:43:07</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>215C_EL PATO</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>98</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3488,7 +3839,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3501,14 +3852,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 17:22:42</t>
+          <t>Última actualización: 17:43:48</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 16</t>
+          <t>Total filas: 17</t>
         </is>
       </c>
     </row>
@@ -3980,6 +4331,33 @@
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>17:43:48</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>19:11</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>215B_LP-P MOR-1 Y 57</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>88</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>L6173</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/horarios-141-2026-01-10.xlsx
+++ b/data/horarios-141-2026-01-10.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G122"/>
+  <dimension ref="A1:G132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 17:43:48</t>
+          <t>Última actualización: 17:54:49</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 117</t>
+          <t>Total filas: 127</t>
         </is>
       </c>
     </row>
@@ -3647,6 +3647,276 @@
       </c>
       <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>17:54:08</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>21</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>17:54:08</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>18:32</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>38</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr"/>
+      <c r="G124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>17:54:08</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>18:34</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>40</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr"/>
+      <c r="G125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>17:54:08</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>18:35</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>14X44_ABASTO</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>41</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr"/>
+      <c r="G126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>17:54:08</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>18:54</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>60</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr"/>
+      <c r="G127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>17:54:08</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>19:03</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>69</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr"/>
+      <c r="G128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>17:54:08</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>19:22</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>215C_EL PATO</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>88</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr"/>
+      <c r="G129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>17:54:08</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>225_GOMEZ</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>96</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>17:54:08</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>19:32</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>215_EL PELIGRO</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>98</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr"/>
+      <c r="G131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>17:54:08</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>19:32</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>27_EL RETIRO</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>98</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr"/>
+      <c r="G132" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3659,7 +3929,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3672,14 +3942,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 17:43:48</t>
+          <t>Última actualización: 17:54:49</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 4</t>
+          <t>Total filas: 6</t>
         </is>
       </c>
     </row>
@@ -3827,6 +4097,60 @@
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>17:54:08</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>19:22</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>215C_EL PATO</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>88</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>17:54:08</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>19:32</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>215_EL PELIGRO</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>98</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3839,7 +4163,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3852,14 +4176,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 17:43:48</t>
+          <t>Última actualización: 17:54:49</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 17</t>
+          <t>Total filas: 18</t>
         </is>
       </c>
     </row>
@@ -4358,6 +4682,33 @@
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>17:54:49</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>19:12</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>215B_LP-P MOR-1 Y 57</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>78</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>L6173</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/horarios-141-2026-01-10.xlsx
+++ b/data/horarios-141-2026-01-10.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G132"/>
+  <dimension ref="A1:G139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 17:54:49</t>
+          <t>Última actualización: 18:18:42</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 127</t>
+          <t>Total filas: 134</t>
         </is>
       </c>
     </row>
@@ -3917,6 +3917,195 @@
       </c>
       <c r="F132" t="inlineStr"/>
       <c r="G132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>18:18:01</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>11_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>7</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr"/>
+      <c r="G133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>18:18:01</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>19:02</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>44</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr"/>
+      <c r="G134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>18:18:01</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>19:06</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>48</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr"/>
+      <c r="G135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>18:18:01</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>19:31</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>215_EL PELIGRO</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>73</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr"/>
+      <c r="G136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>18:18:01</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>19:34</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>76</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr"/>
+      <c r="G137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>18:18:01</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>19:41</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>17X38_ROMERO</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>83</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr"/>
+      <c r="G138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>18:18:01</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>19:52</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>81_EL PELIGRO</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>94</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr"/>
+      <c r="G139" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3929,7 +4118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3942,14 +4131,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 17:54:49</t>
+          <t>Última actualización: 18:18:42</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 6</t>
+          <t>Total filas: 7</t>
         </is>
       </c>
     </row>
@@ -4151,6 +4340,33 @@
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>18:18:01</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>19:31</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>215_EL PELIGRO</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>73</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4163,7 +4379,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4176,14 +4392,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 17:54:49</t>
+          <t>Última actualización: 18:18:42</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 18</t>
+          <t>Total filas: 19</t>
         </is>
       </c>
     </row>
@@ -4709,6 +4925,33 @@
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>18:18:42</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>19:13</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>215B_LP-P MOR-1 Y 57</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>55</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>L6173</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/horarios-141-2026-01-10.xlsx
+++ b/data/horarios-141-2026-01-10.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G139"/>
+  <dimension ref="A1:G156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 18:18:42</t>
+          <t>Última actualización: 18:40:44</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 134</t>
+          <t>Total filas: 151</t>
         </is>
       </c>
     </row>
@@ -4106,6 +4106,465 @@
       </c>
       <c r="F139" t="inlineStr"/>
       <c r="G139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>18:39:58</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>18:44</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>14_ABASTO</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>5</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr"/>
+      <c r="G140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>18:39:58</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>18:53</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>14</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr"/>
+      <c r="G141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>18:39:58</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>19:01</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>17_ROMERO</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>22</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr"/>
+      <c r="G142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>18:39:58</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>26</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr"/>
+      <c r="G143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>18:39:58</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>19:17</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>38</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr"/>
+      <c r="G144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>18:39:58</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>215C_EL PATO</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>41</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr"/>
+      <c r="G145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>18:39:58</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>19:23</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>27_EL RETIRO</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>44</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>18:39:58</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>19:29</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>225_GOMEZ</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>50</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr"/>
+      <c r="G147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>18:39:58</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>215_EL PELIGRO</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>51</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>18:39:58</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>19:33</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>54</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr"/>
+      <c r="G149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>18:39:58</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>17X38_ROMERO</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>61</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr"/>
+      <c r="G150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>18:39:58</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>19:46</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>11_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>67</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr"/>
+      <c r="G151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>18:39:58</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>19:51</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>81_EL PELIGRO</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>72</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr"/>
+      <c r="G152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>18:39:58</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>19:58</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>14X44_ABASTO</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>79</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr"/>
+      <c r="G153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>18:39:58</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>215C_EL PATO</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>81</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr"/>
+      <c r="G154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>18:39:58</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>20:04</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>85</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr"/>
+      <c r="G155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>18:39:58</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>20:14</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>11_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>95</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr"/>
+      <c r="G156" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4118,7 +4577,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4131,14 +4590,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 18:18:42</t>
+          <t>Última actualización: 18:40:44</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 7</t>
+          <t>Total filas: 10</t>
         </is>
       </c>
     </row>
@@ -4367,6 +4826,87 @@
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>18:39:58</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>215C_EL PATO</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>41</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>18:39:58</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>215_EL PELIGRO</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>51</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>18:39:58</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>215C_EL PATO</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>81</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4392,7 +4932,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 18:18:42</t>
+          <t>Última actualización: 18:40:44</t>
         </is>
       </c>
     </row>

--- a/data/horarios-141-2026-01-10.xlsx
+++ b/data/horarios-141-2026-01-10.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G156"/>
+  <dimension ref="A1:G165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 18:40:44</t>
+          <t>Última actualización: 18:51:59</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 151</t>
+          <t>Total filas: 160</t>
         </is>
       </c>
     </row>
@@ -4565,6 +4565,249 @@
       </c>
       <c r="F156" t="inlineStr"/>
       <c r="G156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>18:51:13</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>19:18</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>27</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr"/>
+      <c r="G157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>18:51:13</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>19:26</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>27_EL RETIRO</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>35</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr"/>
+      <c r="G158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>18:51:13</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>19:42</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>51</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr"/>
+      <c r="G159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>18:51:13</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>19:44</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>11_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>53</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr"/>
+      <c r="G160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>18:51:13</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>19:59</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>14X44_ABASTO</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>68</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr"/>
+      <c r="G161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>18:51:13</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>20:01</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>215C_EL PATO</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>70</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr"/>
+      <c r="G162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>18:51:13</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>20:06</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>75</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr"/>
+      <c r="G163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>18:51:13</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>20:26</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>15_ABASTO</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>95</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr"/>
+      <c r="G164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>18:51:13</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>20:29</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>98</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr"/>
+      <c r="G165" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4577,7 +4820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4590,14 +4833,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 18:40:44</t>
+          <t>Última actualización: 18:51:59</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 10</t>
+          <t>Total filas: 11</t>
         </is>
       </c>
     </row>
@@ -4907,6 +5150,33 @@
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>18:51:13</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>20:01</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>215C_EL PATO</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>70</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4932,7 +5202,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 18:40:44</t>
+          <t>Última actualización: 18:51:59</t>
         </is>
       </c>
     </row>

--- a/data/horarios-141-2026-01-10.xlsx
+++ b/data/horarios-141-2026-01-10.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G165"/>
+  <dimension ref="A1:G172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 18:51:59</t>
+          <t>Última actualización: 19:20:10</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 160</t>
+          <t>Total filas: 167</t>
         </is>
       </c>
     </row>
@@ -4808,6 +4808,195 @@
       </c>
       <c r="F165" t="inlineStr"/>
       <c r="G165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>19:19:24</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>19:38</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>19</v>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr"/>
+      <c r="G166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>19:19:24</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>19:41</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>22</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr"/>
+      <c r="G167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>19:19:24</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>19:51</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>32</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr"/>
+      <c r="G168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>19:19:24</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>51</v>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr"/>
+      <c r="G169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>19:19:24</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>20:44</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>215B_EL PATO</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>85</v>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr"/>
+      <c r="G170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>19:19:24</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>20:45</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>17X38_ROMERO</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>86</v>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr"/>
+      <c r="G171" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>19:19:24</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>20:53</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>94</v>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr"/>
+      <c r="G172" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4820,7 +5009,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4833,14 +5022,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 18:51:59</t>
+          <t>Última actualización: 19:20:10</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 11</t>
+          <t>Total filas: 12</t>
         </is>
       </c>
     </row>
@@ -5177,6 +5366,33 @@
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>19:19:24</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>20:44</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>215B_EL PATO</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>85</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5189,7 +5405,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5202,14 +5418,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 18:51:59</t>
+          <t>Última actualización: 19:20:10</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 19</t>
+          <t>Total filas: 20</t>
         </is>
       </c>
     </row>
@@ -5762,6 +5978,33 @@
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>19:20:10</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>19:22</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>215B_LP-P MOR-1 Y 57</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>2</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>L6173</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/horarios-141-2026-01-10.xlsx
+++ b/data/horarios-141-2026-01-10.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G172"/>
+  <dimension ref="A1:G177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 19:20:10</t>
+          <t>Última actualización: 19:44:44</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 167</t>
+          <t>Total filas: 172</t>
         </is>
       </c>
     </row>
@@ -4997,6 +4997,141 @@
       </c>
       <c r="F172" t="inlineStr"/>
       <c r="G172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>19:43:59</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>20:01</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>18</v>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr"/>
+      <c r="G173" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>19:43:59</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>20:28</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>45</v>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr"/>
+      <c r="G174" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>19:43:59</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>20:51</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>68</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr"/>
+      <c r="G175" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>19:43:59</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>21:01</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>215A_EL PATO</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>78</v>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr"/>
+      <c r="G176" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>19:43:59</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>21:09</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>27_EL RETIRO</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>86</v>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr"/>
+      <c r="G177" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5009,7 +5144,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5022,14 +5157,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 19:20:10</t>
+          <t>Última actualización: 19:44:44</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 12</t>
+          <t>Total filas: 13</t>
         </is>
       </c>
     </row>
@@ -5393,6 +5528,33 @@
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>19:43:59</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>21:01</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>215A_EL PATO</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>78</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5405,7 +5567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5418,14 +5580,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 19:20:10</t>
+          <t>Última actualización: 19:44:44</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 20</t>
+          <t>Total filas: 21</t>
         </is>
       </c>
     </row>
@@ -6005,6 +6167,33 @@
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>19:44:19</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>20:42</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>215C_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>58</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>L6203</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/horarios-141-2026-01-10.xlsx
+++ b/data/horarios-141-2026-01-10.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G177"/>
+  <dimension ref="A1:G181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 19:44:44</t>
+          <t>Última actualización: 19:55:41</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 172</t>
+          <t>Total filas: 176</t>
         </is>
       </c>
     </row>
@@ -5132,6 +5132,114 @@
       </c>
       <c r="F177" t="inlineStr"/>
       <c r="G177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>19:54:55</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>20:11</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>17</v>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr"/>
+      <c r="G178" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>19:54:55</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>27</v>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr"/>
+      <c r="G179" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>19:54:55</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>20:50</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>56</v>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr"/>
+      <c r="G180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>19:54:55</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>21:23</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>89</v>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr"/>
+      <c r="G181" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5157,7 +5265,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 19:44:44</t>
+          <t>Última actualización: 19:55:41</t>
         </is>
       </c>
     </row>
@@ -5580,7 +5688,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 19:44:44</t>
+          <t>Última actualización: 19:55:41</t>
         </is>
       </c>
     </row>

--- a/data/horarios-141-2026-01-10.xlsx
+++ b/data/horarios-141-2026-01-10.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G181"/>
+  <dimension ref="A1:G185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 19:55:41</t>
+          <t>Última actualización: 20:19:44</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 176</t>
+          <t>Total filas: 180</t>
         </is>
       </c>
     </row>
@@ -5240,6 +5240,114 @@
       </c>
       <c r="F181" t="inlineStr"/>
       <c r="G181" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>20:18:58</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>20:36</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D182" t="n">
+        <v>18</v>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr"/>
+      <c r="G182" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>20:18:58</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>20:56</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>27_EL RETIRO</t>
+        </is>
+      </c>
+      <c r="D183" t="n">
+        <v>38</v>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr"/>
+      <c r="G183" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>20:18:58</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D184" t="n">
+        <v>82</v>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr"/>
+      <c r="G184" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>20:18:58</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>21:49</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>11_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="D185" t="n">
+        <v>91</v>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr"/>
+      <c r="G185" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5265,7 +5373,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 19:55:41</t>
+          <t>Última actualización: 20:19:44</t>
         </is>
       </c>
     </row>
@@ -5675,7 +5783,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5688,14 +5796,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 19:55:41</t>
+          <t>Última actualización: 20:19:44</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 21</t>
+          <t>Total filas: 23</t>
         </is>
       </c>
     </row>
@@ -6302,6 +6410,60 @@
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>20:19:19</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>20:44</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>215C_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>25</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>L6203</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>20:19:19</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>21:34</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>215C_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>75</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>L6203</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/horarios-141-2026-01-10.xlsx
+++ b/data/horarios-141-2026-01-10.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G185"/>
+  <dimension ref="A1:G189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 20:19:44</t>
+          <t>Última actualización: 20:41:29</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 180</t>
+          <t>Total filas: 184</t>
         </is>
       </c>
     </row>
@@ -5348,6 +5348,114 @@
       </c>
       <c r="F185" t="inlineStr"/>
       <c r="G185" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>20:40:48</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D186" t="n">
+        <v>50</v>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr"/>
+      <c r="G186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>20:40:48</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>21:41</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D187" t="n">
+        <v>61</v>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr"/>
+      <c r="G187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>20:40:48</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>21:56</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>84_COLONIA URQUIZA-ESC 49</t>
+        </is>
+      </c>
+      <c r="D188" t="n">
+        <v>76</v>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr"/>
+      <c r="G188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>20:40:48</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>22:19</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="D189" t="n">
+        <v>99</v>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr"/>
+      <c r="G189" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5373,7 +5481,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 20:19:44</t>
+          <t>Última actualización: 20:41:29</t>
         </is>
       </c>
     </row>
@@ -5783,7 +5891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5796,14 +5904,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 20:19:44</t>
+          <t>Última actualización: 20:41:29</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 23</t>
+          <t>Total filas: 25</t>
         </is>
       </c>
     </row>
@@ -6464,6 +6572,60 @@
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>20:41:29</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>22:13</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>215B_LP-P MOR-1 Y 57</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>92</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>L6173</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>20:41:29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>22:19</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>215A_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>98</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>L6173</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/horarios-141-2026-01-10.xlsx
+++ b/data/horarios-141-2026-01-10.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G189"/>
+  <dimension ref="A1:G194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 20:41:29</t>
+          <t>Última actualización: 20:52:25</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 184</t>
+          <t>Total filas: 189</t>
         </is>
       </c>
     </row>
@@ -5456,6 +5456,141 @@
       </c>
       <c r="F189" t="inlineStr"/>
       <c r="G189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>20:51:44</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>21:02</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>215A_EL PATO</t>
+        </is>
+      </c>
+      <c r="D190" t="n">
+        <v>11</v>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr"/>
+      <c r="G190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>20:51:44</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>21:06</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D191" t="n">
+        <v>15</v>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr"/>
+      <c r="G191" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>20:51:44</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>21:24</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="D192" t="n">
+        <v>33</v>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr"/>
+      <c r="G192" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>20:51:44</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>22:19</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D193" t="n">
+        <v>88</v>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr"/>
+      <c r="G193" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>20:51:44</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>22:22</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D194" t="n">
+        <v>91</v>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr"/>
+      <c r="G194" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5468,7 +5603,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5481,14 +5616,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 20:41:29</t>
+          <t>Última actualización: 20:52:25</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 13</t>
+          <t>Total filas: 14</t>
         </is>
       </c>
     </row>
@@ -5879,6 +6014,33 @@
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>20:51:44</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>21:02</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>215A_EL PATO</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>11</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5904,7 +6066,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 20:41:29</t>
+          <t>Última actualización: 20:52:25</t>
         </is>
       </c>
     </row>

--- a/data/horarios-141-2026-01-10.xlsx
+++ b/data/horarios-141-2026-01-10.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G194"/>
+  <dimension ref="A1:G200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 20:52:25</t>
+          <t>Última actualización: 22:50:18</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 189</t>
+          <t>Total filas: 195</t>
         </is>
       </c>
     </row>
@@ -5591,6 +5591,168 @@
       </c>
       <c r="F194" t="inlineStr"/>
       <c r="G194" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>22:49:33</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>22:52</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>14_ABASTO</t>
+        </is>
+      </c>
+      <c r="D195" t="n">
+        <v>3</v>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr"/>
+      <c r="G195" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>22:49:33</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>23:10</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D196" t="n">
+        <v>21</v>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr"/>
+      <c r="G196" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>22:49:33</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>23:19</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>14_ABASTO</t>
+        </is>
+      </c>
+      <c r="D197" t="n">
+        <v>30</v>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr"/>
+      <c r="G197" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>22:49:33</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>23:31</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D198" t="n">
+        <v>42</v>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr"/>
+      <c r="G198" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>22:49:33</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>23:40</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>215A_EL PATO</t>
+        </is>
+      </c>
+      <c r="D199" t="n">
+        <v>51</v>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr"/>
+      <c r="G199" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>22:49:33</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>23:49</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>11X44_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="D200" t="n">
+        <v>60</v>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr"/>
+      <c r="G200" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5603,7 +5765,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5616,14 +5778,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 20:52:25</t>
+          <t>Última actualización: 22:50:18</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 14</t>
+          <t>Total filas: 15</t>
         </is>
       </c>
     </row>
@@ -6041,6 +6203,33 @@
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>22:49:33</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>23:40</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>215A_EL PATO</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>51</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6053,7 +6242,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6066,14 +6255,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 20:52:25</t>
+          <t>Última actualización: 22:50:18</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 25</t>
+          <t>Total filas: 26</t>
         </is>
       </c>
     </row>
@@ -6788,6 +6977,33 @@
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>22:49:53</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>22:51</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>215C_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>2</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>L6203</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
